--- a/outputs/student-import-test-40/students-40-test.xlsx
+++ b/outputs/student-import-test-40/students-40-test.xlsx
@@ -1,23 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr filterPrivacy="true" defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10830"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFB5C29F-CC39-0341-AAD1-4B4D3298C72C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14805" windowHeight="8010"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="36000" windowHeight="22600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Siswa" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName hidden="true" localSheetId="0" name="_xlnm.Criteria">'Siswa'!$A$1:$D$41</definedName>
+    <definedName name="_xlnm.Criteria" localSheetId="0" hidden="1">Siswa!$A$1:$D$41</definedName>
   </definedNames>
   <calcPr calcId="122211"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="47">
   <si>
     <t>alternativeID</t>
   </si>
@@ -37,9 +38,6 @@
     <t>Ahmad Fauzan</t>
   </si>
   <si>
-    <t>2026/2027 - Semester 1</t>
-  </si>
-  <si>
     <t>KELAS I A</t>
   </si>
   <si>
@@ -158,13 +156,16 @@
   </si>
   <si>
     <t>Zidan Prakoso</t>
+  </si>
+  <si>
+    <t>2020/2021 - Demo</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ap="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties" xmlns:op="http://schemas.openxmlformats.org/officeDocument/2006/custom-properties" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing" xmlns:comp="http://schemas.openxmlformats.org/drawingml/2006/compatibility" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:lc="http://schemas.openxmlformats.org/drawingml/2006/lockedCanvas" xmlns:pic="http://schemas.openxmlformats.org/drawingml/2006/picture" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:sl="http://schemas.openxmlformats.org/schemaLibrary/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xne="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mso="http://schemas.microsoft.com/office/2006/01/customui" xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:cppr="http://schemas.microsoft.com/office/2006/coverPageProps" xmlns:cdip="http://schemas.microsoft.com/office/2006/customDocumentInformationPanel" xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ntns="http://schemas.microsoft.com/office/2006/metadata/customXsn" xmlns:lp="http://schemas.microsoft.com/office/2006/metadata/longProperties" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" xmlns:msink="http://schemas.microsoft.com/ink/2010/main" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" xmlns:cdr14="http://schemas.microsoft.com/office/drawing/2010/chartDrawing" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" xmlns:pic14="http://schemas.microsoft.com/office/drawing/2010/picture" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:dsp="http://schemas.microsoft.com/office/drawing/2008/diagram" xmlns:mso14="http://schemas.microsoft.com/office/2009/07/customui" xmlns:dgm14="http://schemas.microsoft.com/office/drawing/2010/diagram" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x12ac="http://schemas.microsoft.com/office/spreadsheetml/2011/1/ac" xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:xr4="http://schemas.microsoft.com/office/spreadsheetml/2016/revision4" xmlns:xr5="http://schemas.microsoft.com/office/spreadsheetml/2016/revision5" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr7="http://schemas.microsoft.com/office/spreadsheetml/2016/revision7" xmlns:xr8="http://schemas.microsoft.com/office/spreadsheetml/2016/revision8" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr11="http://schemas.microsoft.com/office/spreadsheetml/2016/revision11" xmlns:xr12="http://schemas.microsoft.com/office/spreadsheetml/2016/revision12" xmlns:xr13="http://schemas.microsoft.com/office/spreadsheetml/2016/revision13" xmlns:xr14="http://schemas.microsoft.com/office/spreadsheetml/2016/revision14" xmlns:xr15="http://schemas.microsoft.com/office/spreadsheetml/2016/revision15" xmlns:x16="http://schemas.microsoft.com/office/spreadsheetml/2014/11/main" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:mo="http://schemas.microsoft.com/office/mac/office/2008/main" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:o="urn:schemas-microsoft-com:office:office" xmlns:v="urn:schemas-microsoft-com:vml" mc:Ignorable="c14 cdr14 a14 pic14 x14 xdr14 x14ac dsp mso14 dgm14 x15 x12ac x15ac xr xr2 xr3 xr4 xr5 xr6 xr7 xr8 xr9 xr10 xr11 xr12 xr13 xr14 xr15 x15 x16 x16r2 mo mx mv o v" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -172,7 +173,7 @@
       <family val="2"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
@@ -241,13 +242,13 @@
   </cellStyleXfs>
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -255,12 +256,20 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium2"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -516,18 +525,17 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="true"/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:D41"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col customWidth="true" max="1" min="1" width="20"/>
-    <col customWidth="true" max="2" min="2" width="28"/>
-    <col customWidth="true" max="3" min="3" width="30"/>
-    <col customWidth="true" max="4" min="4" width="18"/>
+    <col min="1" max="1" width="20" customWidth="1"/>
+    <col min="2" max="2" width="28" customWidth="1"/>
+    <col min="3" max="3" width="30" customWidth="1"/>
+    <col min="4" max="4" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="true">
+    <row r="1" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -541,7 +549,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
@@ -549,559 +557,560 @@
         <v>5</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>6</v>
+        <v>46</v>
       </c>
       <c r="D2" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="2" t="s">
+      <c r="C3" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A4" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="3" t="s">
+      <c r="C4" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A5" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" s="2" t="s">
+      <c r="C5" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A6" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" s="3" t="s">
+      <c r="C6" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A7" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B7" s="2" t="s">
+      <c r="C7" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B8" s="3" t="s">
+      <c r="C8" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A9" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B9" s="2" t="s">
+      <c r="C9" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B10" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B10" s="3" t="s">
+      <c r="C10" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A11" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B11" s="2" t="s">
+      <c r="C11" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B12" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B12" s="3" t="s">
+      <c r="C12" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A13" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B13" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C12" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B13" s="2" t="s">
+      <c r="C13" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B14" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C13" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B14" s="3" t="s">
+      <c r="C14" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A15" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B15" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B15" s="2" t="s">
+      <c r="C15" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A16" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B16" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C15" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B16" s="3" t="s">
+      <c r="C16" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A17" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B17" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C16" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B17" s="2" t="s">
+      <c r="C17" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B18" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C17" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B18" s="3" t="s">
+      <c r="C18" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A19" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B19" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C18" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B19" s="2" t="s">
+      <c r="C19" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B20" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C19" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B20" s="3" t="s">
+      <c r="C20" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A21" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B21" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C20" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B21" s="2" t="s">
+      <c r="C21" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B22" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="C21" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B22" s="3" t="s">
+      <c r="C22" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A23" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B23" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C22" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B23" s="2" t="s">
+      <c r="C23" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B24" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C23" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B24" s="3" t="s">
+      <c r="C24" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A25" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B25" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C24" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B25" s="2" t="s">
+      <c r="C25" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B26" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C25" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B26" s="3" t="s">
+      <c r="C26" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A27" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B27" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C26" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B27" s="2" t="s">
+      <c r="C27" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A28" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B28" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="C27" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B28" s="3" t="s">
+      <c r="C28" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A29" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B29" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C28" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B29" s="2" t="s">
+      <c r="C29" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A30" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B30" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C29" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B30" s="3" t="s">
+      <c r="C30" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A31" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B31" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="C30" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D30" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B31" s="2" t="s">
+      <c r="C31" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B32" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C31" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B32" s="3" t="s">
+      <c r="C32" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A33" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B33" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C32" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D32" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B33" s="2" t="s">
+      <c r="C33" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A34" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B34" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C33" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B34" s="3" t="s">
+      <c r="C34" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A35" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B35" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C34" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D34" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B35" s="2" t="s">
+      <c r="C35" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A36" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B36" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C35" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B36" s="3" t="s">
+      <c r="C36" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A37" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B37" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="C36" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D36" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B37" s="2" t="s">
+      <c r="C37" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A38" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B38" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="C37" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B38" s="3" t="s">
+      <c r="C38" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A39" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B39" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="C38" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B39" s="2" t="s">
+      <c r="C39" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A40" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B40" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="C39" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B40" s="3" t="s">
+      <c r="C40" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A41" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B41" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C40" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D40" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B41" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>6</v>
+      <c r="C41" s="3" t="s">
+        <v>46</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="$A$1:$D$41"/>
+  <autoFilter ref="A1:D41" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>